--- a/templates/samples/SALES_AMAZON_SAMPLE.xlsx
+++ b/templates/samples/SALES_AMAZON_SAMPLE.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O27"/>
+  <dimension ref="A1:O28"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1668,9 +1668,56 @@
         <v/>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>2026-07-24</v>
+      </c>
+      <c r="B28" t="str">
+        <v>AMA-SHS-1</v>
+      </c>
+      <c r="C28" t="str">
+        <v>IPH-64GB-GRA</v>
+      </c>
+      <c r="D28" t="str">
+        <v>350100000000000</v>
+      </c>
+      <c r="E28" t="str">
+        <v>NORTHSIDE STOCK</v>
+      </c>
+      <c r="F28">
+        <v>1</v>
+      </c>
+      <c r="G28">
+        <v>206.45</v>
+      </c>
+      <c r="H28">
+        <v>268.39</v>
+      </c>
+      <c r="I28">
+        <v>61.94</v>
+      </c>
+      <c r="J28" t="str">
+        <v/>
+      </c>
+      <c r="K28" t="str">
+        <v/>
+      </c>
+      <c r="L28">
+        <v>8</v>
+      </c>
+      <c r="M28" t="str">
+        <v/>
+      </c>
+      <c r="N28" t="str">
+        <v/>
+      </c>
+      <c r="O28" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O27"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O28"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/templates/samples/SALES_AMAZON_SAMPLE.xlsx
+++ b/templates/samples/SALES_AMAZON_SAMPLE.xlsx
@@ -401,7 +401,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>nw</v>
+        <v>Date</v>
       </c>
       <c r="B1" t="str">
         <v>Order Number</v>

--- a/templates/samples/SALES_AMAZON_SAMPLE.xlsx
+++ b/templates/samples/SALES_AMAZON_SAMPLE.xlsx
@@ -1679,7 +1679,7 @@
         <v>IPH-64GB-GRA</v>
       </c>
       <c r="D28" t="str">
-        <v>350100000000000</v>
+        <v>350190000007777</v>
       </c>
       <c r="E28" t="str">
         <v>NORTHSIDE STOCK</v>

--- a/templates/samples/SALES_AMAZON_SAMPLE.xlsx
+++ b/templates/samples/SALES_AMAZON_SAMPLE.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O28"/>
+  <dimension ref="A1:O23"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -495,16 +495,16 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026-07-05</v>
+        <v>2026-07-06</v>
       </c>
       <c r="B3" t="str">
-        <v>AMA-5004</v>
+        <v>AMA-5005</v>
       </c>
       <c r="C3" t="str">
-        <v>IPH-256GB-PUR</v>
+        <v>SAM-128GB-MID</v>
       </c>
       <c r="D3" t="str">
-        <v>350100000031676</v>
+        <v>350100000039595</v>
       </c>
       <c r="E3" t="str">
         <v>NORTHSIDE STOCK</v>
@@ -513,13 +513,13 @@
         <v>1</v>
       </c>
       <c r="G3">
-        <v>459.49</v>
+        <v>261.54</v>
       </c>
       <c r="H3">
-        <v>653.1</v>
+        <v>348.93</v>
       </c>
       <c r="I3">
-        <v>193.61</v>
+        <v>87.38999999999999</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -542,16 +542,16 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2026-07-09</v>
+        <v>2026-07-11</v>
       </c>
       <c r="B4" t="str">
-        <v>AMA-5008</v>
+        <v>AMA-5010</v>
       </c>
       <c r="C4" t="str">
-        <v>IPH-64GB-PUR</v>
+        <v>IPH-128GB-GRE</v>
       </c>
       <c r="D4" t="str">
-        <v>350100000063352</v>
+        <v>350100000079190</v>
       </c>
       <c r="E4" t="str">
         <v>PHONEBOX DIRECT</v>
@@ -560,13 +560,13 @@
         <v>1</v>
       </c>
       <c r="G4">
-        <v>196.74</v>
+        <v>311.8</v>
       </c>
       <c r="H4">
-        <v>279.91</v>
+        <v>464.89</v>
       </c>
       <c r="I4">
-        <v>83.17000000000002</v>
+        <v>153.08999999999997</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -589,31 +589,31 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2026-07-13</v>
+        <v>2026-07-16</v>
       </c>
       <c r="B5" t="str">
-        <v>AMA-5012</v>
+        <v>AMA-5015</v>
       </c>
       <c r="C5" t="str">
-        <v>SAM-128GB-BLU</v>
+        <v>GOO-128GB-BLA</v>
       </c>
       <c r="D5" t="str">
-        <v>350100000102947</v>
+        <v>350100000118785</v>
       </c>
       <c r="E5" t="str">
-        <v>MOBILE WHOLESALE LTD</v>
+        <v>PHONEBOX DIRECT</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="G5">
-        <v>230.57</v>
+        <v>280.37</v>
       </c>
       <c r="H5">
-        <v>342.69</v>
+        <v>392.6</v>
       </c>
       <c r="I5">
-        <v>112.12</v>
+        <v>112.23000000000002</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -622,7 +622,7 @@
         <v/>
       </c>
       <c r="L5">
-        <v>6.3</v>
+        <v>8</v>
       </c>
       <c r="M5" t="str">
         <v/>
@@ -636,31 +636,31 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2026-07-17</v>
+        <v>2026-07-21</v>
       </c>
       <c r="B6" t="str">
-        <v>AMA-5016</v>
+        <v>AMA-5020</v>
       </c>
       <c r="C6" t="str">
-        <v>IPH-64GB-MID</v>
+        <v>IPH-256GB-GRE</v>
       </c>
       <c r="D6" t="str">
-        <v>350100000126704</v>
+        <v>350100000158380</v>
       </c>
       <c r="E6" t="str">
-        <v>MOBILE WHOLESALE LTD</v>
+        <v>CELLHUB TRADING</v>
       </c>
       <c r="F6">
         <v>1</v>
       </c>
       <c r="G6">
-        <v>212.15</v>
+        <v>469.17</v>
       </c>
       <c r="H6">
-        <v>297.07</v>
+        <v>662.93</v>
       </c>
       <c r="I6">
-        <v>84.91999999999999</v>
+        <v>193.75999999999993</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -669,7 +669,7 @@
         <v/>
       </c>
       <c r="L6">
-        <v>8</v>
+        <v>6.3</v>
       </c>
       <c r="M6" t="str">
         <v/>
@@ -683,31 +683,31 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2026-07-21</v>
+        <v>2026-07-02</v>
       </c>
       <c r="B7" t="str">
-        <v>AMA-5020</v>
+        <v>AMA-5025</v>
       </c>
       <c r="C7" t="str">
-        <v>IPH-256GB-GRE</v>
+        <v>IPH-128GB-STA</v>
       </c>
       <c r="D7" t="str">
-        <v>350100000158380</v>
+        <v>350100000197975</v>
       </c>
       <c r="E7" t="str">
-        <v>CELLHUB TRADING</v>
+        <v>PHONEBOX DIRECT</v>
       </c>
       <c r="F7">
         <v>1</v>
       </c>
       <c r="G7">
-        <v>469.17</v>
+        <v>233.36</v>
       </c>
       <c r="H7">
-        <v>656.42</v>
+        <v>318.95</v>
       </c>
       <c r="I7">
-        <v>187.24999999999994</v>
+        <v>85.58999999999997</v>
       </c>
       <c r="J7" t="str">
         <v/>
@@ -716,7 +716,7 @@
         <v/>
       </c>
       <c r="L7">
-        <v>8</v>
+        <v>6.3</v>
       </c>
       <c r="M7" t="str">
         <v/>
@@ -730,31 +730,31 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2026-07-01</v>
+        <v>2026-07-07</v>
       </c>
       <c r="B8" t="str">
-        <v>AMA-5024</v>
+        <v>AMA-5030</v>
       </c>
       <c r="C8" t="str">
-        <v>IPH-128GB-STA</v>
+        <v>SAM-256GB-GRA</v>
       </c>
       <c r="D8" t="str">
-        <v>350100000197975</v>
+        <v>350100000237570</v>
       </c>
       <c r="E8" t="str">
-        <v>PHONEBOX DIRECT</v>
+        <v>MOBILE WHOLESALE LTD</v>
       </c>
       <c r="F8">
         <v>1</v>
       </c>
       <c r="G8">
-        <v>233.36</v>
+        <v>418.34</v>
       </c>
       <c r="H8">
-        <v>325.62</v>
+        <v>600.73</v>
       </c>
       <c r="I8">
-        <v>92.25999999999999</v>
+        <v>182.39000000000004</v>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -777,31 +777,31 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>2026-07-05</v>
+        <v>2026-07-12</v>
       </c>
       <c r="B9" t="str">
-        <v>AMA-5028</v>
+        <v>AMA-5035</v>
       </c>
       <c r="C9" t="str">
-        <v>IPH-256GB-GRA</v>
+        <v>IPH-256GB-GRE</v>
       </c>
       <c r="D9" t="str">
-        <v>350100000221732</v>
+        <v>350100000277165</v>
       </c>
       <c r="E9" t="str">
-        <v>PHONEBOX DIRECT</v>
+        <v>CELLHUB TRADING</v>
       </c>
       <c r="F9">
         <v>1</v>
       </c>
       <c r="G9">
-        <v>499.6</v>
+        <v>495.98</v>
       </c>
       <c r="H9">
-        <v>721.92</v>
+        <v>737.52</v>
       </c>
       <c r="I9">
-        <v>222.31999999999994</v>
+        <v>241.53999999999996</v>
       </c>
       <c r="J9" t="str">
         <v/>
@@ -810,7 +810,7 @@
         <v/>
       </c>
       <c r="L9">
-        <v>2</v>
+        <v>6.3</v>
       </c>
       <c r="M9" t="str">
         <v/>
@@ -824,31 +824,31 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>2026-07-09</v>
+        <v>2026-07-17</v>
       </c>
       <c r="B10" t="str">
-        <v>AMA-5032</v>
+        <v>AMA-5040</v>
       </c>
       <c r="C10" t="str">
-        <v>IPH-64GB-GRE</v>
+        <v>IPH-64GB-WHI</v>
       </c>
       <c r="D10" t="str">
-        <v>350100000253408</v>
+        <v>350100000316760</v>
       </c>
       <c r="E10" t="str">
-        <v>PHONEBOX DIRECT</v>
+        <v>MOBILE WHOLESALE LTD</v>
       </c>
       <c r="F10">
         <v>1</v>
       </c>
       <c r="G10">
-        <v>196.32</v>
+        <v>192.93</v>
       </c>
       <c r="H10">
-        <v>281.91</v>
+        <v>288.15</v>
       </c>
       <c r="I10">
-        <v>85.59000000000003</v>
+        <v>95.21999999999997</v>
       </c>
       <c r="J10" t="str">
         <v/>
@@ -871,31 +871,31 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2026-07-13</v>
+        <v>2026-07-22</v>
       </c>
       <c r="B11" t="str">
-        <v>AMA-5036</v>
+        <v>AMA-5045</v>
       </c>
       <c r="C11" t="str">
-        <v>SAM-128GB-GRE</v>
+        <v>SAM-128GB-MID</v>
       </c>
       <c r="D11" t="str">
-        <v>350100000293003</v>
+        <v>350100000356355</v>
       </c>
       <c r="E11" t="str">
-        <v>MOBILE WHOLESALE LTD</v>
+        <v>CELLHUB TRADING</v>
       </c>
       <c r="F11">
         <v>1</v>
       </c>
       <c r="G11">
-        <v>262.94</v>
+        <v>237.5</v>
       </c>
       <c r="H11">
-        <v>336.47</v>
+        <v>333.23</v>
       </c>
       <c r="I11">
-        <v>73.53000000000003</v>
+        <v>95.73000000000002</v>
       </c>
       <c r="J11" t="str">
         <v/>
@@ -918,31 +918,31 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>2026-07-17</v>
+        <v>2026-07-03</v>
       </c>
       <c r="B12" t="str">
-        <v>AMA-5040</v>
+        <v>AMA-5050</v>
       </c>
       <c r="C12" t="str">
-        <v>IPH-64GB-WHI</v>
+        <v>IPH-128GB-BLU</v>
       </c>
       <c r="D12" t="str">
-        <v>350100000316760</v>
+        <v>350100000395950</v>
       </c>
       <c r="E12" t="str">
-        <v>MOBILE WHOLESALE LTD</v>
+        <v>PHONEBOX DIRECT</v>
       </c>
       <c r="F12">
         <v>1</v>
       </c>
       <c r="G12">
-        <v>192.93</v>
+        <v>316.67</v>
       </c>
       <c r="H12">
-        <v>286.77</v>
+        <v>443.11</v>
       </c>
       <c r="I12">
-        <v>93.83999999999997</v>
+        <v>126.44</v>
       </c>
       <c r="J12" t="str">
         <v/>
@@ -951,7 +951,7 @@
         <v/>
       </c>
       <c r="L12">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M12" t="str">
         <v/>
@@ -965,16 +965,16 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2026-07-21</v>
+        <v>2026-07-08</v>
       </c>
       <c r="B13" t="str">
-        <v>AMA-5044</v>
+        <v>AMA-5055</v>
       </c>
       <c r="C13" t="str">
-        <v>IPH-256GB-MID</v>
+        <v>GOO-128GB-MID</v>
       </c>
       <c r="D13" t="str">
-        <v>350100000348436</v>
+        <v>350100000435545</v>
       </c>
       <c r="E13" t="str">
         <v>MOBILE WHOLESALE LTD</v>
@@ -983,13 +983,13 @@
         <v>1</v>
       </c>
       <c r="G13">
-        <v>484.06</v>
+        <v>267</v>
       </c>
       <c r="H13">
-        <v>718.37</v>
+        <v>377.39</v>
       </c>
       <c r="I13">
-        <v>234.31</v>
+        <v>110.38999999999999</v>
       </c>
       <c r="J13" t="str">
         <v/>
@@ -1012,31 +1012,31 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>2026-07-01</v>
+        <v>2026-07-13</v>
       </c>
       <c r="B14" t="str">
-        <v>AMA-5048</v>
+        <v>AMA-5060</v>
       </c>
       <c r="C14" t="str">
-        <v>IPH-128GB-BLA</v>
+        <v>SAM-128GB-WHI</v>
       </c>
       <c r="D14" t="str">
-        <v>350100000388031</v>
+        <v>350100000483059</v>
       </c>
       <c r="E14" t="str">
-        <v>NORTHSIDE STOCK</v>
+        <v>MOBILE WHOLESALE LTD</v>
       </c>
       <c r="F14">
         <v>1</v>
       </c>
       <c r="G14">
-        <v>232.81</v>
+        <v>250.16</v>
       </c>
       <c r="H14">
-        <v>326.65</v>
+        <v>335.89</v>
       </c>
       <c r="I14">
-        <v>93.83999999999997</v>
+        <v>85.72999999999999</v>
       </c>
       <c r="J14" t="str">
         <v/>
@@ -1059,31 +1059,31 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>2026-07-05</v>
+        <v>2026-07-18</v>
       </c>
       <c r="B15" t="str">
-        <v>AMA-5052</v>
+        <v>AMA-5065</v>
       </c>
       <c r="C15" t="str">
-        <v>IPH-256GB-PUR</v>
+        <v>IPH-128GB-WHI</v>
       </c>
       <c r="D15" t="str">
-        <v>350100000411788</v>
+        <v>350100000514735</v>
       </c>
       <c r="E15" t="str">
-        <v>MOBILE WHOLESALE LTD</v>
+        <v>PHONEBOX DIRECT</v>
       </c>
       <c r="F15">
         <v>1</v>
       </c>
       <c r="G15">
-        <v>497.17</v>
+        <v>222.24</v>
       </c>
       <c r="H15">
-        <v>681.49</v>
+        <v>294.66</v>
       </c>
       <c r="I15">
-        <v>184.32</v>
+        <v>72.42000000000002</v>
       </c>
       <c r="J15" t="str">
         <v/>
@@ -1092,7 +1092,7 @@
         <v/>
       </c>
       <c r="L15">
-        <v>8</v>
+        <v>6.3</v>
       </c>
       <c r="M15" t="str">
         <v/>
@@ -1106,31 +1106,31 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>2026-07-09</v>
+        <v>2026-07-23</v>
       </c>
       <c r="B16" t="str">
-        <v>AMA-5056</v>
+        <v>AMA-5070</v>
       </c>
       <c r="C16" t="str">
-        <v>IPH-64GB-MID</v>
+        <v>SAM-256GB-GRA</v>
       </c>
       <c r="D16" t="str">
-        <v>350100000443464</v>
+        <v>350100000554330</v>
       </c>
       <c r="E16" t="str">
-        <v>MOBILE WHOLESALE LTD</v>
+        <v>CELLHUB TRADING</v>
       </c>
       <c r="F16">
         <v>1</v>
       </c>
       <c r="G16">
-        <v>194.75</v>
+        <v>451.39</v>
       </c>
       <c r="H16">
-        <v>269.01</v>
+        <v>574.19</v>
       </c>
       <c r="I16">
-        <v>74.25999999999999</v>
+        <v>122.80000000000007</v>
       </c>
       <c r="J16" t="str">
         <v/>
@@ -1139,7 +1139,7 @@
         <v/>
       </c>
       <c r="L16">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M16" t="str">
         <v/>
@@ -1153,31 +1153,31 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>2026-07-13</v>
+        <v>2026-07-04</v>
       </c>
       <c r="B17" t="str">
-        <v>AMA-5060</v>
+        <v>AMA-5075</v>
       </c>
       <c r="C17" t="str">
-        <v>SAM-128GB-WHI</v>
+        <v>IPH-256GB-BLA</v>
       </c>
       <c r="D17" t="str">
-        <v>350100000483059</v>
+        <v>350100000593925</v>
       </c>
       <c r="E17" t="str">
-        <v>MOBILE WHOLESALE LTD</v>
+        <v>NORTHSIDE STOCK</v>
       </c>
       <c r="F17">
         <v>1</v>
       </c>
       <c r="G17">
-        <v>250.16</v>
+        <v>501.14</v>
       </c>
       <c r="H17">
-        <v>325.93</v>
+        <v>631.55</v>
       </c>
       <c r="I17">
-        <v>75.77000000000001</v>
+        <v>130.40999999999997</v>
       </c>
       <c r="J17" t="str">
         <v/>
@@ -1200,16 +1200,16 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>2026-07-17</v>
+        <v>2026-07-09</v>
       </c>
       <c r="B18" t="str">
-        <v>AMA-5064</v>
+        <v>AMA-5080</v>
       </c>
       <c r="C18" t="str">
-        <v>IPH-64GB-GRE</v>
+        <v>IPH-64GB-WHI</v>
       </c>
       <c r="D18" t="str">
-        <v>350100000506816</v>
+        <v>350100000633520</v>
       </c>
       <c r="E18" t="str">
         <v>MOBILE WHOLESALE LTD</v>
@@ -1218,13 +1218,13 @@
         <v>1</v>
       </c>
       <c r="G18">
-        <v>197.28</v>
+        <v>190.34</v>
       </c>
       <c r="H18">
-        <v>264.89</v>
+        <v>275.79</v>
       </c>
       <c r="I18">
-        <v>67.60999999999999</v>
+        <v>85.45000000000002</v>
       </c>
       <c r="J18" t="str">
         <v/>
@@ -1233,7 +1233,7 @@
         <v/>
       </c>
       <c r="L18">
-        <v>8</v>
+        <v>6.3</v>
       </c>
       <c r="M18" t="str">
         <v/>
@@ -1247,31 +1247,31 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>2026-07-21</v>
+        <v>2026-07-14</v>
       </c>
       <c r="B19" t="str">
-        <v>AMA-5068</v>
+        <v>AMA-5085</v>
       </c>
       <c r="C19" t="str">
-        <v>IPH-256GB-MID</v>
+        <v>SAM-128GB-GRA</v>
       </c>
       <c r="D19" t="str">
-        <v>350100000538492</v>
+        <v>350100000673115</v>
       </c>
       <c r="E19" t="str">
-        <v>MOBILE WHOLESALE LTD</v>
+        <v>NORTHSIDE STOCK</v>
       </c>
       <c r="F19">
         <v>1</v>
       </c>
       <c r="G19">
-        <v>482.51</v>
+        <v>246.21</v>
       </c>
       <c r="H19">
-        <v>620.19</v>
+        <v>319.55</v>
       </c>
       <c r="I19">
-        <v>137.68000000000006</v>
+        <v>73.34</v>
       </c>
       <c r="J19" t="str">
         <v/>
@@ -1294,31 +1294,31 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>2026-07-01</v>
+        <v>2026-07-19</v>
       </c>
       <c r="B20" t="str">
-        <v>AMA-5072</v>
+        <v>AMA-5090</v>
       </c>
       <c r="C20" t="str">
-        <v>IPH-128GB-MID</v>
+        <v>IPH-128GB-GRA</v>
       </c>
       <c r="D20" t="str">
-        <v>350100000578087</v>
+        <v>350100007839810</v>
       </c>
       <c r="E20" t="str">
-        <v>NORTHSIDE STOCK</v>
+        <v>PHONEBOX DIRECT</v>
       </c>
       <c r="F20">
         <v>1</v>
       </c>
       <c r="G20">
-        <v>222.91</v>
+        <v>335.04</v>
       </c>
       <c r="H20">
-        <v>285.35</v>
+        <v>494.65</v>
       </c>
       <c r="I20">
-        <v>62.440000000000026</v>
+        <v>159.60999999999996</v>
       </c>
       <c r="J20" t="str">
         <v/>
@@ -1327,7 +1327,7 @@
         <v/>
       </c>
       <c r="L20">
-        <v>8</v>
+        <v>6.3</v>
       </c>
       <c r="M20" t="str">
         <v/>
@@ -1341,16 +1341,16 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>2026-07-05</v>
+        <v>2026-07-24</v>
       </c>
       <c r="B21" t="str">
-        <v>AMA-5076</v>
+        <v>AMA-5095</v>
       </c>
       <c r="C21" t="str">
-        <v>IPH-256GB-STA</v>
+        <v>GOO-128GB-BLU</v>
       </c>
       <c r="D21" t="str">
-        <v>350100000601844</v>
+        <v>350100007879405</v>
       </c>
       <c r="E21" t="str">
         <v>MOBILE WHOLESALE LTD</v>
@@ -1359,13 +1359,13 @@
         <v>1</v>
       </c>
       <c r="G21">
-        <v>476.5</v>
+        <v>293.74</v>
       </c>
       <c r="H21">
-        <v>688.88</v>
+        <v>406.06</v>
       </c>
       <c r="I21">
-        <v>212.38</v>
+        <v>112.32</v>
       </c>
       <c r="J21" t="str">
         <v/>
@@ -1388,31 +1388,31 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>2026-07-09</v>
+        <v>2026-07-01</v>
       </c>
       <c r="B22" t="str">
-        <v>AMA-5080</v>
+        <v>AMA-5000</v>
       </c>
       <c r="C22" t="str">
-        <v>IPH-64GB-WHI</v>
+        <v>IPH-128GB-GRA</v>
       </c>
       <c r="D22" t="str">
-        <v>350100000633520</v>
+        <v>350100000007919</v>
       </c>
       <c r="E22" t="str">
-        <v>MOBILE WHOLESALE LTD</v>
+        <v>PHONEBOX DIRECT</v>
       </c>
       <c r="F22">
         <v>1</v>
       </c>
       <c r="G22">
-        <v>190.34</v>
+        <v>234.13</v>
       </c>
       <c r="H22">
-        <v>239.87</v>
+        <v>319.21</v>
       </c>
       <c r="I22">
-        <v>49.53</v>
+        <v>85.07999999999998</v>
       </c>
       <c r="J22" t="str">
         <v/>
@@ -1421,7 +1421,7 @@
         <v/>
       </c>
       <c r="L22">
-        <v>6.3</v>
+        <v>8</v>
       </c>
       <c r="M22" t="str">
         <v/>
@@ -1435,16 +1435,16 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>2026-07-13</v>
+        <v>2026-07-24</v>
       </c>
       <c r="B23" t="str">
-        <v>AMA-5084</v>
+        <v>AMA-SHS-1</v>
       </c>
       <c r="C23" t="str">
-        <v>SAM-128GB-GRA</v>
+        <v>IPH-64GB-GRA</v>
       </c>
       <c r="D23" t="str">
-        <v>350100000673115</v>
+        <v>350190000007777</v>
       </c>
       <c r="E23" t="str">
         <v>NORTHSIDE STOCK</v>
@@ -1453,13 +1453,13 @@
         <v>1</v>
       </c>
       <c r="G23">
-        <v>246.21</v>
+        <v>206.45</v>
       </c>
       <c r="H23">
-        <v>318</v>
+        <v>268.39</v>
       </c>
       <c r="I23">
-        <v>71.78999999999999</v>
+        <v>61.94</v>
       </c>
       <c r="J23" t="str">
         <v/>
@@ -1468,7 +1468,7 @@
         <v/>
       </c>
       <c r="L23">
-        <v>6.3</v>
+        <v>8</v>
       </c>
       <c r="M23" t="str">
         <v/>
@@ -1477,247 +1477,12 @@
         <v/>
       </c>
       <c r="O23" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="str">
-        <v>2026-07-17</v>
-      </c>
-      <c r="B24" t="str">
-        <v>AMA-5088</v>
-      </c>
-      <c r="C24" t="str">
-        <v>IPH-64GB-STA</v>
-      </c>
-      <c r="D24" t="str">
-        <v>350100000696872</v>
-      </c>
-      <c r="E24" t="str">
-        <v>NORTHSIDE STOCK</v>
-      </c>
-      <c r="F24">
-        <v>1</v>
-      </c>
-      <c r="G24">
-        <v>186.57</v>
-      </c>
-      <c r="H24">
-        <v>239.7</v>
-      </c>
-      <c r="I24">
-        <v>53.129999999999995</v>
-      </c>
-      <c r="J24" t="str">
-        <v/>
-      </c>
-      <c r="K24" t="str">
-        <v/>
-      </c>
-      <c r="L24">
-        <v>8</v>
-      </c>
-      <c r="M24" t="str">
-        <v/>
-      </c>
-      <c r="N24" t="str">
-        <v/>
-      </c>
-      <c r="O24" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="str">
-        <v>2026-07-21</v>
-      </c>
-      <c r="B25" t="str">
-        <v>AMA-5092</v>
-      </c>
-      <c r="C25" t="str">
-        <v>IPH-256GB-GRA</v>
-      </c>
-      <c r="D25" t="str">
-        <v>350100007855648</v>
-      </c>
-      <c r="E25" t="str">
-        <v>PHONEBOX DIRECT</v>
-      </c>
-      <c r="F25">
-        <v>1</v>
-      </c>
-      <c r="G25">
-        <v>462.92</v>
-      </c>
-      <c r="H25">
-        <v>615.58</v>
-      </c>
-      <c r="I25">
-        <v>152.66000000000003</v>
-      </c>
-      <c r="J25" t="str">
-        <v/>
-      </c>
-      <c r="K25" t="str">
-        <v/>
-      </c>
-      <c r="L25">
-        <v>2</v>
-      </c>
-      <c r="M25" t="str">
-        <v/>
-      </c>
-      <c r="N25" t="str">
-        <v/>
-      </c>
-      <c r="O25" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="str">
-        <v>2026-07-01</v>
-      </c>
-      <c r="B26" t="str">
-        <v>AMA-5096</v>
-      </c>
-      <c r="C26" t="str">
-        <v>IPH-128GB-GRA</v>
-      </c>
-      <c r="D26" t="str">
-        <v>350100007887324</v>
-      </c>
-      <c r="E26" t="str">
-        <v>PHONEBOX DIRECT</v>
-      </c>
-      <c r="F26">
-        <v>1</v>
-      </c>
-      <c r="G26">
-        <v>223.04</v>
-      </c>
-      <c r="H26">
-        <v>329.29</v>
-      </c>
-      <c r="I26">
-        <v>106.25000000000003</v>
-      </c>
-      <c r="J26" t="str">
-        <v/>
-      </c>
-      <c r="K26" t="str">
-        <v/>
-      </c>
-      <c r="L26">
-        <v>6.3</v>
-      </c>
-      <c r="M26" t="str">
-        <v/>
-      </c>
-      <c r="N26" t="str">
-        <v/>
-      </c>
-      <c r="O26" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="str">
-        <v>2026-07-01</v>
-      </c>
-      <c r="B27" t="str">
-        <v>AMA-5000</v>
-      </c>
-      <c r="C27" t="str">
-        <v>IPH-128GB-GRA</v>
-      </c>
-      <c r="D27" t="str">
-        <v>350100000007919</v>
-      </c>
-      <c r="E27" t="str">
-        <v>PHONEBOX DIRECT</v>
-      </c>
-      <c r="F27">
-        <v>1</v>
-      </c>
-      <c r="G27">
-        <v>234.13</v>
-      </c>
-      <c r="H27">
-        <v>319.21</v>
-      </c>
-      <c r="I27">
-        <v>85.07999999999998</v>
-      </c>
-      <c r="J27" t="str">
-        <v/>
-      </c>
-      <c r="K27" t="str">
-        <v/>
-      </c>
-      <c r="L27">
-        <v>8</v>
-      </c>
-      <c r="M27" t="str">
-        <v/>
-      </c>
-      <c r="N27" t="str">
-        <v/>
-      </c>
-      <c r="O27" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="str">
-        <v>2026-07-24</v>
-      </c>
-      <c r="B28" t="str">
-        <v>AMA-SHS-1</v>
-      </c>
-      <c r="C28" t="str">
-        <v>IPH-64GB-GRA</v>
-      </c>
-      <c r="D28" t="str">
-        <v>350190000007777</v>
-      </c>
-      <c r="E28" t="str">
-        <v>NORTHSIDE STOCK</v>
-      </c>
-      <c r="F28">
-        <v>1</v>
-      </c>
-      <c r="G28">
-        <v>206.45</v>
-      </c>
-      <c r="H28">
-        <v>268.39</v>
-      </c>
-      <c r="I28">
-        <v>61.94</v>
-      </c>
-      <c r="J28" t="str">
-        <v/>
-      </c>
-      <c r="K28" t="str">
-        <v/>
-      </c>
-      <c r="L28">
-        <v>8</v>
-      </c>
-      <c r="M28" t="str">
-        <v/>
-      </c>
-      <c r="N28" t="str">
-        <v/>
-      </c>
-      <c r="O28" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O28"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O23"/>
   </ignoredErrors>
 </worksheet>
 </file>